--- a/Logic/Question_Binder_Sep30.xlsx
+++ b/Logic/Question_Binder_Sep30.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
-  <x:workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gosciminski/Documents/GitHub/M-GRAT/Logic/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335B057B-E7C8-B949-9864-2F0BB0810F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <x:bookViews>
-    <x:workbookView xWindow="21740" yWindow="-20580" windowWidth="33720" windowHeight="19440" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="README" sheetId="1" r:id="rId1"/>
-    <x:sheet name="Question Manifest" sheetId="2" r:id="rId2"/>
-    <x:sheet name="Objectives" sheetId="3" r:id="rId3"/>
-    <x:sheet name="Obstacles" sheetId="4" r:id="rId4"/>
-    <x:sheet name="Milestone Qs — Group" sheetId="5" r:id="rId5"/>
-    <x:sheet name="Milestone Qs — Multiselect" sheetId="6" r:id="rId6"/>
-    <x:sheet name="Milestone Qs — Ladder" sheetId="7" r:id="rId7"/>
-    <x:sheet name="Growth Appetite" sheetId="8" r:id="rId8"/>
-    <x:sheet name="Scoring" sheetId="9" r:id="rId9"/>
-  </x:sheets>
-  <x:calcPr calcId="0"/>
-</x:workbook>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D2A2C9-6D43-F849-A64A-078B8CBD8A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="21740" yWindow="-21000" windowWidth="33720" windowHeight="19380" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="README" sheetId="1" r:id="rId1"/>
+    <sheet name="Question Manifest" sheetId="2" r:id="rId2"/>
+    <sheet name="Objectives" sheetId="3" r:id="rId3"/>
+    <sheet name="Obstacles" sheetId="4" r:id="rId4"/>
+    <sheet name="Milestone Qs — Group" sheetId="5" r:id="rId5"/>
+    <sheet name="Milestone Qs — Multiselect" sheetId="6" r:id="rId6"/>
+    <sheet name="Milestone Qs — Ladder" sheetId="7" r:id="rId7"/>
+    <sheet name="Growth Appetite" sheetId="8" r:id="rId8"/>
+    <sheet name="Scoring" sheetId="9" r:id="rId9"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="566">
   <si>
     <t>MAXIMO APPLICATION SUITE (MAS) READINESS ASSESSMENT — SCORING &amp; RULES SPECIFICATION</t>
   </si>
@@ -306,14 +306,6 @@
     <t>Sum(Dimension_Score_i * Weight_i) for i in [1..8]</t>
   </si>
   <si>
-    <t>Weighted average across the 8 active scored dimensions: Asset Data (15%), Work Mgmt (15%), Inspections (10%), Supply Chain (10%), Reliability (15%), Condition Monitoring (15%), Scheduling (10%), Assignment (10%).
-• 0–24%: Level 1 (Unstructured / Reactive)
-• 25–49%: Level 2 (Core Operations / Baseline)
-• 50–74%: Level 3 (Connected / Condition-Informed)
-• 75–89%: Level 4 (Predictive / Optimized)
-• 90–100%: Level 5 (Prescriptive &amp; Automated)</t>
-  </si>
-  <si>
     <t>Current APM Stage</t>
   </si>
   <si>
@@ -326,15 +318,6 @@
     <t>Highest Stage N where All Gating Milestones for Stage N == MET</t>
   </si>
   <si>
-    <t>Deterministic Stage Gating Rule:
-• APM Stage 1 (Digital Foundation): Requires AD-1-REG, AD-1-CRIT, CM-1-LF, RP-1-FC = MET
-• APM Stage 2 (APM Foundation): Requires Stage 1 Met + AD-2-CLAS, CM-2-HLTH, CM-2-MON, RP-2-RS, RP-3-FMEA = MET
-• APM Stage 3 (CBM+): Requires Stage 2 Met + AD-2-HIER, IC-3-METB, CM-2-TRIG, CM-3-IOT, CM-3-MVAR, SC-4-OPT = MET
-• APM Stage 4 (Predictive): Requires Stage 3 Met + CM-4-PRED, CM-5-RCBF, CM-6-LCFDBK, RP-4-RCBF = MET
-• APM Stage 5 (Prescriptive): Requires Stage 4 Met + RP-5-FGOV = MET
-* If Stage 1 gating milestones are not all Met, Current Stage = APM 1 (In Progress).</t>
-  </si>
-  <si>
     <t>Current FSM Stage</t>
   </si>
   <si>
@@ -342,15 +325,6 @@
   </si>
   <si>
     <t>Milestone status (MET/UNMET) for all FSM gating milestones</t>
-  </si>
-  <si>
-    <t>Deterministic Stage Gating Rule:
-• FSM Stage 1 (Reactive Execution): Requires AD-1-REG, WM-1-JPBASIC, IC-1-PROG, SCH-1-DATES, AS-1-OWN, SC-1-REG, WA-1-BAS = MET
-• FSM Stage 2 (Coordinated Operations): Requires Stage 1 Met + AD-1-CRIT, AD-2-CLAS, WM-2-JPNEEDS, IC-2-INSB, SCH-2-FWD, AS-2-CENT, WA-2-ACT, SC-2-BASICS = MET
-• FSM Stage 3 (Structured Scheduling): Requires Stage 2 Met + AD-2-HIER, WM-3-JPAR, IC-3-METB, CM-2-TRIG, SCH-3-CONS, AS-3-BEST, WA-3-EFF, SC-3-PLAN = MET
-• FSM Stage 4 (Intelligent Field Coord): Requires Stage 3 Met + SC-4-OPT = MET (Advanced scheduling/dispatch active)
-• FSM Stage 5 (Optimized Field Ops): Requires Stage 4 Met
-* If Stage 1 gating milestones are not all Met, Current Stage = FSM 1 (In Progress).</t>
   </si>
   <si>
     <t>Top Met Milestones (Strengths)</t>
@@ -1687,295 +1661,413 @@
   <si>
     <t>Acts as the primary context tie-breaker (obstacle_match: 2 = Primary, 1 = Secondary) among equally ready foundational milestones, and populates "Why" attribution tags. No boost applied</t>
   </si>
+  <si>
+    <t>Customer-facing interpretation</t>
+  </si>
+  <si>
+    <t>Seller notes</t>
+  </si>
+  <si>
+    <t>Budget is in place. Your roadmap prioritises the actions with the fastest time to value this year.</t>
+  </si>
+  <si>
+    <t>Strong signal. Lead with scoping and ROI conversation this quarter.</t>
+  </si>
+  <si>
+    <t>Budget is being considered. Your roadmap is designed to help build the case alongside the plan.</t>
+  </si>
+  <si>
+    <t>Approval cycle is the constraint. Provide a business case template and follow up after the budget decision.</t>
+  </si>
+  <si>
+    <t>No budget is in place yet. Your roadmap focuses on the value story you would need to bring to leadership.</t>
+  </si>
+  <si>
+    <t>Nurture track. Lead with value and case studies. Re-qualify in 30–60 days.</t>
+  </si>
+  <si>
+    <t>You have leadership backing. That makes it much easier to move recommendations into action.</t>
+  </si>
+  <si>
+    <t>Executive is engaged. Offer a leadership briefing or exec summary version of the report.</t>
+  </si>
+  <si>
+    <t>Leadership interest is there, but not yet formalised. Building that sponsorship is likely your most important next step.</t>
+  </si>
+  <si>
+    <t>Help build the sponsor. Share the report with the interested leader to give them something concrete to rally around.</t>
+  </si>
+  <si>
+    <t>There is no leadership sponsor yet. Without one, expansion decisions are hard to progress — this is worth addressing before anything else.</t>
+  </si>
+  <si>
+    <t>Risk flag. Ask who the right leader to engage is before progressing the conversation.</t>
+  </si>
+  <si>
+    <t>You have active plans in motion. Your roadmap connects directly to where that initiative should focus.</t>
+  </si>
+  <si>
+    <t>Near-term opportunity. Recommend starting a scoping exercise immediately.</t>
+  </si>
+  <si>
+    <t>Conversations are happening but nothing is committed yet. Your roadmap can help turn that discussion into a concrete starting point.</t>
+  </si>
+  <si>
+    <t>Exploratory stage. Offer a discovery workshop or a more detailed assessment session.</t>
+  </si>
+  <si>
+    <t>There are no active plans right now. Your roadmap gives you a clear picture to come back to when the timing is right.</t>
+  </si>
+  <si>
+    <t>Long cycle. Follow up in 60–90 days with relevant content. No pressure close.</t>
+  </si>
+  <si>
+    <t>Your organisation moves quickly when the value is clear. Your roadmap leads with the actions that can show results fast.</t>
+  </si>
+  <si>
+    <t>Foreground quick wins. Highlight Stage 1→2 milestones with fast time-to-value.</t>
+  </si>
+  <si>
+    <t>You work within a planned investment cycle. Your roadmap is structured as a phased journey that fits that rhythm.</t>
+  </si>
+  <si>
+    <t>Standard roadmap framing. Emphasise the phased approach and stage-by-stage progression.</t>
+  </si>
+  <si>
+    <t>Your organisation takes a longer view on technology investment. Your roadmap frames the full multi-stage journey and the cumulative value it builds.</t>
+  </si>
+  <si>
+    <t>Lead with strategic framing. Emphasise cumulative ROI across the full journey, not just the next step.</t>
+  </si>
+  <si>
+    <t>Weighted average across the 8 active scored dimensions: Asset Data (15%), Work Mgmt (15%), Inspections (10%), Supply Chain (10%), Reliability (15%), Condition Monitoring (15%), Scheduling (10%), Assignment (10%).
+• 0–24%: Level 1 (Foundational)
+• 25–49%: Level 2 (Core Operations)
+• 50–74%: Level 3 (Connected)
+• 75–89%: Level 4 (Optimized)
+• 90–100%: Level 5 (Prescriptive &amp; Automated)</t>
+  </si>
+  <si>
+    <t>Deterministic Stage Gating Rule:
+• APM Stage 1 (Digital Maintenance Foundation): Requires AD-1-REG, AD-1-CRIT, CM-1-LF, RP-1-FC = MET
+• APM Stage 2 (APM Foundation): Requires Stage 1 Met + AD-2-CLAS, CM-2-HLTH, RP-2-RS, RP-3-FMEA = MET
+• APM Stage 3 (Maintenance Optimisation (CBM+)): Requires Stage 2 Met + AD-2-HIER, IC-3-METB, CM-2-TRIG, CM-3-IOT, CM-3-MVAR, SC-4-OPT = MET
+• APM Stage 4 (Prescriptive Reliability): Requires Stage 3 Met + CM-4-PRED, CM-5-RCBF, CM-6-LCFDBK, RP-4-RCBF = MET
+• APM Stage 5 (Reliability Enterprise): Requires Stage 4 Met + RP-5-FGOV = MET
+* If Stage 1 gating milestones are not all Met, Current Stage = APM 1 (In Progress).</t>
+  </si>
+  <si>
+    <t>Deterministic Stage Gating Rule:
+• FSM Stage 1 (Reactive Execution): Requires WM-1-JPBASIC, SCH-1-DATES, WA-1-BAS = MET
+• FSM Stage 2 (Coordinated Operations): Requires Stage 1 Met + AD-1-CRIT, AD-2-CLAS, WM-2-JPNEEDS, IC-2-INSB, SCH-2-FWD, AS-2-CENT, WA-2-ACT, SC-2-BASICS = MET
+• FSM Stage 3 (Structured Scheduling): Requires Stage 2 Met + AD-2-HIER, WM-3-JPAR, IC-3-METB, CM-2-TRIG, SCH-3-CONS, AS-3-BEST, WA-3-EFF, SC-3-PLAN = MET
+• FSM Stage 4 (Intelligent Field Coord): Requires Stage 3 Met + SC-4-OPT = MET (Advanced scheduling/dispatch active)
+• FSM Stage 5 (Optimized Field Ops): Requires Stage 4 Met
+* If Stage 1 gating milestones are not all Met, Current Stage = FSM 1 (In Progress).</t>
+  </si>
+  <si>
+    <t>Notes: KG - I removed the CM-2-MON milestone because 1) Monitor isn't required for APM at all and 2) that milestone has no question associated with it in the binder so it was breaking this stage calculation.  I think we could remove more.  
+Open issue: We should  consider a different way of detecting current stage for APM since there are so many different ways to do things.  Or possibly we need to genericize the milestones so they say things like "a mechanism triggers work based on condition signals" and then we explain the multiple ways to do that.</t>
+  </si>
+  <si>
+    <t>Notes: KG - I removed some milestones from each stage, incl asset data, inventory and inspections ones.  They are recommended but not required.  
+Open issue: We need to figure out a better system for associating required vs recommended milestones with the journey stages.  The milestone_register shows which stage a milestone is most likely to be associated with but it was not intended to be a list of required milestones.  I suspect this populated from there, so we need to sanity check it.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <x:fonts count="14" x14ac:knownFonts="1">
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FF1F3864"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:sz val="9.5"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="14"/>
-      <x:color rgb="FF0043CE"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="10"/>
-      <x:color rgb="FF525252"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="9"/>
-      <x:color rgb="FF525252"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="9.5"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-      <x:family xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" val="2"/>
-      <x:scheme xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" val="2"/>
-      <x:scheme xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" val="minor"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="10">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1F3864"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD9E1F2"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF2F2F2"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF2CC"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF0043CE"/>
-        <x:bgColor rgb="FF0043CE"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1F2328"/>
-        <x:bgColor rgb="FF1F2328"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF4F4F4"/>
-        <x:bgColor rgb="FFF4F4F4"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="3">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFBFBFBF"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFBFBFBF"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFBFBFBF"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFBFBFBF"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D7DE"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD0D7DE"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D7DE"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D7DE"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="30">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="right" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" indent="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </x:cellStyles>
-  <x:dxfs count="0"/>
-  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <x:extLst>
-    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="13" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0043CE"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF525252"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF525252"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="10">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0043CE"/>
+        <bgColor rgb="FF0043CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F2328"/>
+        <bgColor rgb="FF1F2328"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F4F4"/>
+        <bgColor rgb="FFF4F4F4"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="4">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D7DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D7DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D7DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D7DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D7DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D7DE"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="31">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </x:ext>
-    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </x:ext>
-  </x:extLst>
-</x:styleSheet>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2275,7 +2367,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -2283,12 +2375,12 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -2296,23 +2388,23 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -2321,109 +2413,109 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B10" s="2"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2452,45 +2544,45 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
@@ -2500,25 +2592,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="G3" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -2529,20 +2621,20 @@
         <v>16</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -2554,25 +2646,25 @@
         <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -2583,20 +2675,20 @@
         <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -2608,20 +2700,20 @@
         <v>16</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -2633,23 +2725,23 @@
         <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -2660,25 +2752,25 @@
         <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -2689,20 +2781,20 @@
         <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -2714,22 +2806,22 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E11" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G11" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -2740,22 +2832,22 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E12" t="s">
         <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G12" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H12" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -2766,22 +2858,22 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D13" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E13" t="s">
         <v>35</v>
       </c>
       <c r="F13" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G13" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H13" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -2792,7 +2884,7 @@
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D14" t="s">
         <v>50</v>
@@ -2801,13 +2893,13 @@
         <v>52</v>
       </c>
       <c r="F14" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G14" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H14" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -2818,22 +2910,22 @@
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D15" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
       </c>
       <c r="F15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G15" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H15" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -2844,22 +2936,22 @@
         <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D16" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E16" t="s">
         <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G16" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H16" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2870,25 +2962,25 @@
         <v>40</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>235</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2899,23 +2991,23 @@
         <v>40</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2926,23 +3018,23 @@
         <v>40</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2953,23 +3045,23 @@
         <v>40</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.2">
@@ -2980,25 +3072,25 @@
         <v>40</v>
       </c>
       <c r="C21" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="I21" s="11" t="s">
         <v>246</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="45" x14ac:dyDescent="0.2">
@@ -3009,25 +3101,25 @@
         <v>40</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="G22" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="H22" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="I22" s="11" t="s">
         <v>251</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3035,28 +3127,28 @@
         <v>21</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H23" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="I23" s="11" t="s">
         <v>256</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3064,23 +3156,23 @@
         <v>22</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D24" s="11"/>
       <c r="E24" s="11" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I24" s="11"/>
     </row>
@@ -3089,23 +3181,23 @@
         <v>23</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="11" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I25" s="11"/>
     </row>
@@ -3114,23 +3206,23 @@
         <v>24</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I26" s="11"/>
     </row>
@@ -3163,77 +3255,77 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>203</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>530</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
+      <c r="A2" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="H3" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>276</v>
       </c>
       <c r="J3" s="4"/>
     </row>
@@ -3244,16 +3336,16 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>277</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>280</v>
       </c>
       <c r="J4" s="5"/>
     </row>
@@ -3264,16 +3356,16 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J5" s="4"/>
     </row>
@@ -3284,16 +3376,16 @@
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>284</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>287</v>
       </c>
       <c r="J6" s="5"/>
     </row>
@@ -3304,16 +3396,16 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J7" s="4"/>
     </row>
@@ -3324,16 +3416,16 @@
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>291</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>294</v>
       </c>
       <c r="J8" s="5"/>
     </row>
@@ -3344,16 +3436,16 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="J9" s="4"/>
     </row>
@@ -3364,16 +3456,16 @@
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J10" s="5"/>
     </row>
@@ -3384,16 +3476,16 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J11" s="4"/>
     </row>
@@ -3425,70 +3517,70 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>203</v>
-      </c>
     </row>
     <row r="2" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>531</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="A2" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>308</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -3498,16 +3590,16 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I4" s="5"/>
     </row>
@@ -3517,16 +3609,16 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -3536,16 +3628,16 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="I6" s="5"/>
     </row>
@@ -3555,16 +3647,16 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -3574,16 +3666,16 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I8" s="5"/>
     </row>
@@ -3593,16 +3685,16 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -3612,16 +3704,16 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>329</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>332</v>
       </c>
       <c r="I10" s="5"/>
     </row>
@@ -3631,16 +3723,16 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>334</v>
-      </c>
       <c r="H11" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="I11" s="4"/>
     </row>
@@ -3674,397 +3766,397 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="H1" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="I3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G7" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="I7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="J7" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B8" t="s">
         <v>221</v>
-      </c>
-      <c r="B8" t="s">
-        <v>224</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
       </c>
       <c r="D8" t="s">
+        <v>359</v>
+      </c>
+      <c r="E8" t="s">
+        <v>360</v>
+      </c>
+      <c r="F8" t="s">
+        <v>361</v>
+      </c>
+      <c r="G8" t="s">
+        <v>343</v>
+      </c>
+      <c r="H8" t="s">
+        <v>344</v>
+      </c>
+      <c r="I8" t="s">
+        <v>345</v>
+      </c>
+      <c r="J8" t="s">
         <v>362</v>
-      </c>
-      <c r="E8" t="s">
-        <v>363</v>
-      </c>
-      <c r="F8" t="s">
-        <v>364</v>
-      </c>
-      <c r="G8" t="s">
-        <v>346</v>
-      </c>
-      <c r="H8" t="s">
-        <v>347</v>
-      </c>
-      <c r="I8" t="s">
-        <v>348</v>
-      </c>
-      <c r="J8" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C9" t="s">
         <v>16</v>
       </c>
       <c r="D9" t="s">
+        <v>363</v>
+      </c>
+      <c r="E9" t="s">
+        <v>364</v>
+      </c>
+      <c r="F9" t="s">
+        <v>365</v>
+      </c>
+      <c r="G9" t="s">
+        <v>343</v>
+      </c>
+      <c r="H9" t="s">
+        <v>344</v>
+      </c>
+      <c r="I9" t="s">
+        <v>345</v>
+      </c>
+      <c r="J9" t="s">
         <v>366</v>
-      </c>
-      <c r="E9" t="s">
-        <v>367</v>
-      </c>
-      <c r="F9" t="s">
-        <v>368</v>
-      </c>
-      <c r="G9" t="s">
-        <v>346</v>
-      </c>
-      <c r="H9" t="s">
-        <v>347</v>
-      </c>
-      <c r="I9" t="s">
-        <v>348</v>
-      </c>
-      <c r="J9" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="J10" s="11" t="s">
         <v>370</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>239</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="J12" s="11" t="s">
         <v>377</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>379</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="J13" s="11" t="s">
         <v>381</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>383</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -4099,50 +4191,50 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="27" t="s">
         <v>385</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>388</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
@@ -4155,25 +4247,25 @@
         <v>28</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>392</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -4187,22 +4279,22 @@
         <v>28</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>393</v>
-      </c>
       <c r="I4" s="4" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J4" s="4"/>
     </row>
@@ -4217,25 +4309,25 @@
         <v>28</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -4249,23 +4341,23 @@
         <v>28</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -4279,25 +4371,25 @@
         <v>34</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="H7" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>406</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -4311,22 +4403,22 @@
         <v>34</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -4341,22 +4433,22 @@
         <v>34</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -4371,25 +4463,25 @@
         <v>34</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -4403,28 +4495,28 @@
         <v>34</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>40</v>
@@ -4433,30 +4525,30 @@
         <v>45</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H12" s="10" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>40</v>
@@ -4465,30 +4557,30 @@
         <v>45</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>420</v>
-      </c>
       <c r="G13" s="10" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="H13" s="10" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>40</v>
@@ -4497,30 +4589,30 @@
         <v>45</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H14" s="10" t="b">
         <v>0</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -4529,30 +4621,30 @@
         <v>45</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H15" s="10" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>40</v>
@@ -4561,30 +4653,30 @@
         <v>45</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H16" s="10" t="b">
         <v>0</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>40</v>
@@ -4593,28 +4685,28 @@
         <v>45</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="10" t="b">
         <v>1</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>40</v>
@@ -4623,30 +4715,30 @@
         <v>45</v>
       </c>
       <c r="D18" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>431</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>432</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>434</v>
       </c>
       <c r="H18" s="12" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>40</v>
@@ -4655,30 +4747,30 @@
         <v>45</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="H19" s="12" t="b">
         <v>0</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>40</v>
@@ -4687,30 +4779,30 @@
         <v>45</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H20" s="12" t="b">
         <v>0</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>40</v>
@@ -4719,30 +4811,30 @@
         <v>45</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H21" s="12" t="b">
         <v>0</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>40</v>
@@ -4751,25 +4843,25 @@
         <v>45</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H22" s="12" t="b">
         <v>1</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -4806,54 +4898,54 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="27" t="s">
         <v>445</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>448</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
     </row>
     <row r="3" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
@@ -4866,26 +4958,26 @@
         <v>50</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F3" s="4">
         <v>0</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -4899,28 +4991,28 @@
         <v>50</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F4" s="5">
         <v>1</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -4934,28 +5026,28 @@
         <v>50</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F5" s="4">
         <v>2</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -4969,28 +5061,28 @@
         <v>50</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F6" s="5">
         <v>3</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5004,25 +5096,25 @@
         <v>57</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F7" s="6">
         <v>0</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5036,28 +5128,28 @@
         <v>57</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F8" s="6">
         <v>1</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5071,28 +5163,28 @@
         <v>57</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F9" s="6">
         <v>2</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5106,28 +5198,28 @@
         <v>57</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F10" s="6">
         <v>3</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5141,25 +5233,25 @@
         <v>62</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F11" s="6">
         <v>0</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5173,28 +5265,28 @@
         <v>62</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F12" s="6">
         <v>1</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5208,28 +5300,28 @@
         <v>62</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F13" s="6">
         <v>2</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5243,28 +5335,28 @@
         <v>62</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F14" s="6">
         <v>3</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -5276,380 +5368,379 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0700-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:tabColor rgb="FFA9D18E"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:J14"/>
-  <x:sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <x:cols>
-    <x:col min="1" max="1" width="12" style="6" customWidth="1"/>
-    <x:col min="2" max="2" width="44" style="6" customWidth="1"/>
-    <x:col min="3" max="3" width="16" style="6" customWidth="1"/>
-    <x:col min="4" max="4" width="38" style="6" customWidth="1"/>
-    <x:col min="5" max="5" width="36" style="6" customWidth="1"/>
-    <x:col min="6" max="6" width="16" style="6" customWidth="1"/>
-    <x:col min="7" max="7" width="28" style="6" customWidth="1"/>
-    <x:col min="8" max="8" width="38" style="6" customWidth="1"/>
-    <x:col min="9" max="9" width="52" style="6" customWidth="1"/>
-    <x:col min="10" max="10" width="52" style="6" customWidth="1"/>
-    <x:col min="11" max="16384" width="8.83203125" style="6"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <x:c r="A1" s="3" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="s">
-        <x:v>486</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="s">
-        <x:v>487</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>Customer-facing interpretation</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>Seller notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A2" s="25" t="s">
-        <x:v>488</x:v>
-      </x:c>
-      <x:c r="B2" s="26"/>
-      <x:c r="C2" s="26"/>
-      <x:c r="D2" s="26"/>
-      <x:c r="E2" s="26"/>
-      <x:c r="F2" s="26"/>
-      <x:c r="G2" s="26"/>
-      <x:c r="H2" s="26"/>
-    </x:row>
-    <x:row r="3" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A3" s="4" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="B3" s="4" t="s">
-        <x:v>489</x:v>
-      </x:c>
-      <x:c r="C3" s="4" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="D3" s="4" t="s">
-        <x:v>491</x:v>
-      </x:c>
-      <x:c r="E3" s="4" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="F3" s="7">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G3" s="4" t="s">
-        <x:v>493</x:v>
-      </x:c>
-      <x:c r="H3" s="4" t="s">
-        <x:v>494</x:v>
-      </x:c>
-      <x:c r="I3" s="28" t="str">
-        <x:v>Budget is in place. Your roadmap prioritises the actions with the fastest time to value this year.</x:v>
-      </x:c>
-      <x:c r="J3" s="28" t="str">
-        <x:v>Strong signal. Lead with scoping and ROI conversation this quarter.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A4" s="4" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="B4" s="4"/>
-      <x:c r="C4" s="4"/>
-      <x:c r="D4" s="4"/>
-      <x:c r="E4" s="4" t="s">
-        <x:v>495</x:v>
-      </x:c>
-      <x:c r="F4" s="7">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="s">
-        <x:v>496</x:v>
-      </x:c>
-      <x:c r="H4" s="4"/>
-      <x:c r="I4" s="28" t="str">
-        <x:v>Budget is being considered. Your roadmap is designed to help build the case alongside the plan.</x:v>
-      </x:c>
-      <x:c r="J4" s="28" t="str">
-        <x:v>Approval cycle is the constraint. Provide a business case template and follow up after the budget decision.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A5" s="4" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="B5" s="4"/>
-      <x:c r="C5" s="4"/>
-      <x:c r="D5" s="4"/>
-      <x:c r="E5" s="4" t="s">
-        <x:v>497</x:v>
-      </x:c>
-      <x:c r="F5" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="4" t="s">
-        <x:v>498</x:v>
-      </x:c>
-      <x:c r="H5" s="4" t="s">
-        <x:v>499</x:v>
-      </x:c>
-      <x:c r="I5" s="28" t="str">
-        <x:v>No budget is in place yet. Your roadmap focuses on the value story you would need to bring to leadership.</x:v>
-      </x:c>
-      <x:c r="J5" s="28" t="str">
-        <x:v>Nurture track. Lead with value and case studies. Re-qualify in 30–60 days.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A6" s="6" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="s">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="s">
-        <x:v>501</x:v>
-      </x:c>
-      <x:c r="E6" s="6" t="s">
-        <x:v>502</x:v>
-      </x:c>
-      <x:c r="F6" s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G6" s="6" t="s">
-        <x:v>503</x:v>
-      </x:c>
-      <x:c r="H6" s="6" t="s">
-        <x:v>504</x:v>
-      </x:c>
-      <x:c r="I6" s="28" t="str">
-        <x:v>You have leadership backing. That makes it much easier to move recommendations into action.</x:v>
-      </x:c>
-      <x:c r="J6" s="28" t="str">
-        <x:v>Executive is engaged. Offer a leadership briefing or exec summary version of the report.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A7" s="6" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="E7" s="6" t="s">
-        <x:v>505</x:v>
-      </x:c>
-      <x:c r="F7" s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="s">
-        <x:v>506</x:v>
-      </x:c>
-      <x:c r="I7" s="28" t="str">
-        <x:v>Leadership interest is there, but not yet formalised. Building that sponsorship is likely your most important next step.</x:v>
-      </x:c>
-      <x:c r="J7" s="28" t="str">
-        <x:v>Help build the sponsor. Share the report with the interested leader to give them something concrete to rally around.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A8" s="6" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="E8" s="6" t="s">
-        <x:v>507</x:v>
-      </x:c>
-      <x:c r="F8" s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="6" t="s">
-        <x:v>508</x:v>
-      </x:c>
-      <x:c r="H8" s="6" t="s">
-        <x:v>499</x:v>
-      </x:c>
-      <x:c r="I8" s="28" t="str">
-        <x:v>There is no leadership sponsor yet. Without one, expansion decisions are hard to progress — this is worth addressing before anything else.</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="str">
-        <x:v>Risk flag. Ask who the right leader to engage is before progressing the conversation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A9" s="6" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>509</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="D9" s="6" t="s">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="E9" s="6" t="s">
-        <x:v>511</x:v>
-      </x:c>
-      <x:c r="F9" s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G9" s="6" t="s">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="H9" s="6" t="s">
-        <x:v>513</x:v>
-      </x:c>
-      <x:c r="I9" s="28" t="str">
-        <x:v>You have active plans in motion. Your roadmap connects directly to where that initiative should focus.</x:v>
-      </x:c>
-      <x:c r="J9" s="28" t="str">
-        <x:v>Near-term opportunity. Recommend starting a scoping exercise immediately.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A10" s="6" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="E10" s="6" t="s">
-        <x:v>514</x:v>
-      </x:c>
-      <x:c r="F10" s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G10" s="6" t="s">
-        <x:v>515</x:v>
-      </x:c>
-      <x:c r="I10" s="28" t="str">
-        <x:v>Conversations are happening but nothing is committed yet. Your roadmap can help turn that discussion into a concrete starting point.</x:v>
-      </x:c>
-      <x:c r="J10" s="28" t="str">
-        <x:v>Exploratory stage. Offer a discovery workshop or a more detailed assessment session.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A11" s="6" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="E11" s="6" t="s">
-        <x:v>516</x:v>
-      </x:c>
-      <x:c r="F11" s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="6" t="s">
-        <x:v>517</x:v>
-      </x:c>
-      <x:c r="H11" s="6" t="s">
-        <x:v>518</x:v>
-      </x:c>
-      <x:c r="I11" s="28" t="str">
-        <x:v>There are no active plans right now. Your roadmap gives you a clear picture to come back to when the timing is right.</x:v>
-      </x:c>
-      <x:c r="J11" s="28" t="str">
-        <x:v>Long cycle. Follow up in 60–90 days with relevant content. No pressure close.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A12" s="6" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="s">
-        <x:v>519</x:v>
-      </x:c>
-      <x:c r="C12" s="6" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="D12" s="6" t="s">
-        <x:v>520</x:v>
-      </x:c>
-      <x:c r="E12" s="6" t="s">
-        <x:v>521</x:v>
-      </x:c>
-      <x:c r="F12" s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G12" s="6" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="I12" s="28" t="str">
-        <x:v>Your organisation moves quickly when the value is clear. Your roadmap leads with the actions that can show results fast.</x:v>
-      </x:c>
-      <x:c r="J12" s="28" t="str">
-        <x:v>Foreground quick wins. Highlight Stage 1→2 milestones with fast time-to-value.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A13" s="6" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="E13" s="6" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="F13" s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G13" s="6" t="s">
-        <x:v>524</x:v>
-      </x:c>
-      <x:c r="I13" s="28" t="str">
-        <x:v>You work within a planned investment cycle. Your roadmap is structured as a phased journey that fits that rhythm.</x:v>
-      </x:c>
-      <x:c r="J13" s="28" t="str">
-        <x:v>Standard roadmap framing. Emphasise the phased approach and stage-by-stage progression.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A14" s="6" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="E14" s="6" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="F14" s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="6" t="s">
-        <x:v>526</x:v>
-      </x:c>
-      <x:c r="H14" s="6" t="s">
-        <x:v>527</x:v>
-      </x:c>
-      <x:c r="I14" s="28" t="str">
-        <x:v>Your organisation takes a longer view on technology investment. Your roadmap frames the full multi-stage journey and the cumulative value it builds.</x:v>
-      </x:c>
-      <x:c r="J14" s="28" t="str">
-        <x:v>Lead with strategic framing. Emphasise cumulative ROI across the full journey, not just the next step.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells count="1">
-    <x:mergeCell ref="A2:H2"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFA9D18E"/>
+  </sheetPr>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12" style="6" customWidth="1"/>
+    <col min="2" max="2" width="44" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16" style="6" customWidth="1"/>
+    <col min="4" max="4" width="38" style="6" customWidth="1"/>
+    <col min="5" max="5" width="36" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16" style="6" customWidth="1"/>
+    <col min="7" max="7" width="28" style="6" customWidth="1"/>
+    <col min="8" max="8" width="38" style="6" customWidth="1"/>
+    <col min="9" max="10" width="52" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="8.83203125" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>535</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="27" t="s">
+        <v>485</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+    </row>
+    <row r="3" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="F3" s="7">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>537</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="F4" s="7">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="21" t="s">
+        <v>539</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>541</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="F6" s="8">
+        <v>2</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>543</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>545</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>547</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="F9" s="8">
+        <v>2</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>549</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>551</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>553</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="F12" s="8">
+        <v>2</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>560</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5672,18 +5763,18 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
@@ -6102,18 +6193,18 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
@@ -6131,6 +6222,9 @@
       <c r="E20" s="16" t="s">
         <v>87</v>
       </c>
+      <c r="F20" s="30" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="135" x14ac:dyDescent="0.2">
       <c r="A21" s="20" t="s">
@@ -6146,290 +6240,296 @@
         <v>91</v>
       </c>
       <c r="E21" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="210" x14ac:dyDescent="0.2">
+      <c r="A22" s="20" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="195" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="B22" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="C22" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="D22" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="E22" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="210" x14ac:dyDescent="0.2">
+      <c r="A23" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="B23" s="20" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="225" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
+      <c r="C23" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>100</v>
-      </c>
       <c r="D23" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>101</v>
+        <v>563</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.2">
       <c r="A24" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="E24" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="21" t="s">
-        <v>536</v>
-      </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
+      <c r="A26" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="E27" s="16" t="s">
         <v>108</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A28" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="E28" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="105" x14ac:dyDescent="0.2">
       <c r="A29" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B29" s="20" t="s">
+      <c r="E29" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="240" x14ac:dyDescent="0.2">
       <c r="A30" s="20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="135" x14ac:dyDescent="0.2">
       <c r="A31" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B31" s="20" t="s">
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="C31" s="11" t="s">
-        <v>534</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="E34" s="16" t="s">
         <v>130</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="45" x14ac:dyDescent="0.2">
       <c r="A35" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="E35" s="11" t="s">
         <v>135</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="75" x14ac:dyDescent="0.2">
       <c r="A36" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="E36" s="11" t="s">
         <v>140</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="75" x14ac:dyDescent="0.2">
       <c r="A37" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37" s="11" t="s">
         <v>144</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.2">
       <c r="A38" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="E38" s="11" t="s">
         <v>149</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A39" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>153</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>537</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.2">
       <c r="A40" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="E40" s="11" t="s">
         <v>158</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/Logic/Question_Binder_Sep30.xlsx
+++ b/Logic/Question_Binder_Sep30.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gosciminski/Documents/GitHub/M-GRAT/Logic/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D2A2C9-6D43-F849-A64A-078B8CBD8A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3720676F-6F82-B94B-A282-53CB36FF9783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21740" yWindow="-21000" windowWidth="33720" windowHeight="19380" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21740" yWindow="-20160" windowWidth="33720" windowHeight="19380" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="565">
   <si>
     <t>MAXIMO APPLICATION SUITE (MAS) READINESS ASSESSMENT — SCORING &amp; RULES SPECIFICATION</t>
   </si>
@@ -494,9 +494,6 @@
   </si>
   <si>
     <t>Multi-select friction points / obstacles</t>
-  </si>
-  <si>
-    <t>No boost applied</t>
   </si>
   <si>
     <t>Direct tie-breaker for candidate recommendations.</t>
@@ -1749,15 +1746,6 @@
   </si>
   <si>
     <t>Deterministic Stage Gating Rule:
-• APM Stage 1 (Digital Maintenance Foundation): Requires AD-1-REG, AD-1-CRIT, CM-1-LF, RP-1-FC = MET
-• APM Stage 2 (APM Foundation): Requires Stage 1 Met + AD-2-CLAS, CM-2-HLTH, RP-2-RS, RP-3-FMEA = MET
-• APM Stage 3 (Maintenance Optimisation (CBM+)): Requires Stage 2 Met + AD-2-HIER, IC-3-METB, CM-2-TRIG, CM-3-IOT, CM-3-MVAR, SC-4-OPT = MET
-• APM Stage 4 (Prescriptive Reliability): Requires Stage 3 Met + CM-4-PRED, CM-5-RCBF, CM-6-LCFDBK, RP-4-RCBF = MET
-• APM Stage 5 (Reliability Enterprise): Requires Stage 4 Met + RP-5-FGOV = MET
-* If Stage 1 gating milestones are not all Met, Current Stage = APM 1 (In Progress).</t>
-  </si>
-  <si>
-    <t>Deterministic Stage Gating Rule:
 • FSM Stage 1 (Reactive Execution): Requires WM-1-JPBASIC, SCH-1-DATES, WA-1-BAS = MET
 • FSM Stage 2 (Coordinated Operations): Requires Stage 1 Met + AD-1-CRIT, AD-2-CLAS, WM-2-JPNEEDS, IC-2-INSB, SCH-2-FWD, AS-2-CENT, WA-2-ACT, SC-2-BASICS = MET
 • FSM Stage 3 (Structured Scheduling): Requires Stage 2 Met + AD-2-HIER, WM-3-JPAR, IC-3-METB, CM-2-TRIG, SCH-3-CONS, AS-3-BEST, WA-3-EFF, SC-3-PLAN = MET
@@ -1766,12 +1754,21 @@
 * If Stage 1 gating milestones are not all Met, Current Stage = FSM 1 (In Progress).</t>
   </si>
   <si>
-    <t>Notes: KG - I removed the CM-2-MON milestone because 1) Monitor isn't required for APM at all and 2) that milestone has no question associated with it in the binder so it was breaking this stage calculation.  I think we could remove more.  
-Open issue: We should  consider a different way of detecting current stage for APM since there are so many different ways to do things.  Or possibly we need to genericize the milestones so they say things like "a mechanism triggers work based on condition signals" and then we explain the multiple ways to do that.</t>
-  </si>
-  <si>
     <t>Notes: KG - I removed some milestones from each stage, incl asset data, inventory and inspections ones.  They are recommended but not required.  
 Open issue: We need to figure out a better system for associating required vs recommended milestones with the journey stages.  The milestone_register shows which stage a milestone is most likely to be associated with but it was not intended to be a list of required milestones.  I suspect this populated from there, so we need to sanity check it.</t>
+  </si>
+  <si>
+    <t>Deterministic Stage Gating Rule:
+• APM Stage 1 (Digital Maintenance Foundation): Requires AD-1-REG, AD-1-CRIT, CM-1-LF, RP-1-FC = MET
+• APM Stage 2 (APM Foundation): Requires Stage 1 Met + AD-2-CLAS, CM-2-HLTH, RP-2-RS, RP-3-FMEA = MET
+• APM Stage 3 (Maintenance Optimisation (CBM+)): Requires Stage 2 Met + AD-2-HIER, IC-3-METB, CM-2-TRIG, CM-3-IOT, CM-3-MVAR, SC-4-OPT = MET
+• APM Stage 4 (Prescriptive Reliability): Requires Stage 3 Met + CM-4-PRED, CM-6-LCFDBK, RP-4-RCBF = MET
+• APM Stage 5 (Reliability Enterprise): Requires Stage 4 Met + RP-5-FGOV = MET
+* If Stage 1 gating milestones are not all Met, Current Stage = APM 1 (In Progress).</t>
+  </si>
+  <si>
+    <t>Notes: KG - I removed the CM-2-MON milestone because 1) Monitor isn't required for APM at all and 2) that milestone has no question associated with it in the binder so it was breaking this stage calculation.  I think we could remove more.  Removed CM-5-RCBFbc it's not covered in questions.
+Open issue: We should  consider a different way of detecting current stage for APM since there are so many different ways to do things.  Or possibly we need to genericize the milestones so they say things like "a mechanism triggers work based on condition signals" and then we explain the multiple ways to do that.</t>
   </si>
 </sst>
 </file>
@@ -2031,6 +2028,12 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2046,12 +2049,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2367,7 +2364,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -2375,12 +2372,12 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -2388,23 +2385,23 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -2413,109 +2410,109 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B10" s="2"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2544,45 +2541,45 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>126</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="I1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="27" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
     </row>
     <row r="3" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
@@ -2592,25 +2589,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -2621,20 +2618,20 @@
         <v>16</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>209</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -2646,25 +2643,25 @@
         <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>131</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -2675,20 +2672,20 @@
         <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>131</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -2700,20 +2697,20 @@
         <v>16</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>131</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -2725,23 +2722,23 @@
         <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>131</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -2752,25 +2749,25 @@
         <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>131</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -2781,20 +2778,20 @@
         <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>131</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -2806,22 +2803,22 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F11" t="s">
         <v>131</v>
       </c>
       <c r="G11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -2832,10 +2829,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" t="s">
         <v>223</v>
-      </c>
-      <c r="D12" t="s">
-        <v>224</v>
       </c>
       <c r="E12" t="s">
         <v>30</v>
@@ -2844,10 +2841,10 @@
         <v>136</v>
       </c>
       <c r="G12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -2858,10 +2855,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" t="s">
         <v>225</v>
-      </c>
-      <c r="D13" t="s">
-        <v>226</v>
       </c>
       <c r="E13" t="s">
         <v>35</v>
@@ -2870,10 +2867,10 @@
         <v>136</v>
       </c>
       <c r="G13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -2884,7 +2881,7 @@
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D14" t="s">
         <v>50</v>
@@ -2896,10 +2893,10 @@
         <v>141</v>
       </c>
       <c r="G14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -2910,10 +2907,10 @@
         <v>51</v>
       </c>
       <c r="C15" t="s">
+        <v>227</v>
+      </c>
+      <c r="D15" t="s">
         <v>228</v>
-      </c>
-      <c r="D15" t="s">
-        <v>229</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
@@ -2922,10 +2919,10 @@
         <v>141</v>
       </c>
       <c r="G15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -2936,10 +2933,10 @@
         <v>51</v>
       </c>
       <c r="C16" t="s">
+        <v>229</v>
+      </c>
+      <c r="D16" t="s">
         <v>230</v>
-      </c>
-      <c r="D16" t="s">
-        <v>231</v>
       </c>
       <c r="E16" t="s">
         <v>65</v>
@@ -2948,10 +2945,10 @@
         <v>141</v>
       </c>
       <c r="G16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2962,25 +2959,25 @@
         <v>40</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>233</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>234</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>131</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2991,23 +2988,23 @@
         <v>40</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>131</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3018,23 +3015,23 @@
         <v>40</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>131</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3045,23 +3042,23 @@
         <v>40</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>131</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.2">
@@ -3072,25 +3069,25 @@
         <v>40</v>
       </c>
       <c r="C21" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="E21" s="11" t="s">
         <v>244</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>245</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>136</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="45" x14ac:dyDescent="0.2">
@@ -3101,25 +3098,25 @@
         <v>40</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>248</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>249</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>136</v>
       </c>
       <c r="G22" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="I22" s="11" t="s">
         <v>250</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3127,28 +3124,28 @@
         <v>21</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="D23" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="D23" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="E23" s="11" t="s">
+      <c r="F23" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="H23" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="H23" s="11" t="s">
+      <c r="I23" s="11" t="s">
         <v>255</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3156,23 +3153,23 @@
         <v>22</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>252</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>253</v>
       </c>
       <c r="D24" s="11"/>
       <c r="E24" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I24" s="11"/>
     </row>
@@ -3181,23 +3178,23 @@
         <v>23</v>
       </c>
       <c r="B25" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>252</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>253</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I25" s="11"/>
     </row>
@@ -3206,23 +3203,23 @@
         <v>24</v>
       </c>
       <c r="B26" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>252</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>253</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I26" s="11"/>
     </row>
@@ -3255,77 +3252,77 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>126</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="J1" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>527</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
+      <c r="A2" s="27" t="s">
+        <v>526</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
     </row>
     <row r="3" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>273</v>
       </c>
       <c r="J3" s="4"/>
     </row>
@@ -3336,16 +3333,16 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>276</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>277</v>
       </c>
       <c r="J4" s="5"/>
     </row>
@@ -3356,16 +3353,16 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="J5" s="4"/>
     </row>
@@ -3376,16 +3373,16 @@
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>283</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>284</v>
       </c>
       <c r="J6" s="5"/>
     </row>
@@ -3396,16 +3393,16 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>287</v>
       </c>
       <c r="J7" s="4"/>
     </row>
@@ -3416,16 +3413,16 @@
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>290</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>291</v>
       </c>
       <c r="J8" s="5"/>
     </row>
@@ -3436,16 +3433,16 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>293</v>
       </c>
       <c r="J9" s="4"/>
     </row>
@@ -3456,16 +3453,16 @@
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>294</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>295</v>
       </c>
       <c r="J10" s="5"/>
     </row>
@@ -3476,16 +3473,16 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>297</v>
       </c>
       <c r="J11" s="4"/>
     </row>
@@ -3517,70 +3514,70 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>126</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>263</v>
-      </c>
       <c r="F1" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>299</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>528</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
+      <c r="A2" s="27" t="s">
+        <v>527</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
     </row>
     <row r="3" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>305</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -3590,16 +3587,16 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>307</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>308</v>
       </c>
       <c r="I4" s="5"/>
     </row>
@@ -3609,16 +3606,16 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>312</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -3628,16 +3625,16 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>314</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>315</v>
       </c>
       <c r="I6" s="5"/>
     </row>
@@ -3647,16 +3644,16 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>319</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -3666,16 +3663,16 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>321</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>322</v>
       </c>
       <c r="I8" s="5"/>
     </row>
@@ -3685,16 +3682,16 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>325</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -3704,16 +3701,16 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>328</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>329</v>
       </c>
       <c r="I10" s="5"/>
     </row>
@@ -3723,16 +3720,16 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="I11" s="4"/>
     </row>
@@ -3766,397 +3763,397 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="28" t="s">
         <v>338</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26" t="s">
-        <v>339</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F3" t="s">
         <v>353</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>342</v>
+      </c>
+      <c r="H3" t="s">
+        <v>343</v>
+      </c>
+      <c r="I3" t="s">
+        <v>344</v>
+      </c>
+      <c r="J3" t="s">
         <v>354</v>
-      </c>
-      <c r="G3" t="s">
-        <v>343</v>
-      </c>
-      <c r="H3" t="s">
-        <v>344</v>
-      </c>
-      <c r="I3" t="s">
-        <v>345</v>
-      </c>
-      <c r="J3" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>349</v>
-      </c>
       <c r="G5" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>345</v>
       </c>
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>352</v>
-      </c>
       <c r="G6" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>345</v>
       </c>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B7" t="s">
         <v>218</v>
-      </c>
-      <c r="B7" t="s">
-        <v>219</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E7" t="s">
+        <v>355</v>
+      </c>
+      <c r="F7" t="s">
         <v>356</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>342</v>
+      </c>
+      <c r="H7" t="s">
+        <v>343</v>
+      </c>
+      <c r="I7" t="s">
+        <v>344</v>
+      </c>
+      <c r="J7" t="s">
         <v>357</v>
-      </c>
-      <c r="G7" t="s">
-        <v>343</v>
-      </c>
-      <c r="H7" t="s">
-        <v>344</v>
-      </c>
-      <c r="I7" t="s">
-        <v>345</v>
-      </c>
-      <c r="J7" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
       </c>
       <c r="D8" t="s">
+        <v>358</v>
+      </c>
+      <c r="E8" t="s">
         <v>359</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>360</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>342</v>
+      </c>
+      <c r="H8" t="s">
+        <v>343</v>
+      </c>
+      <c r="I8" t="s">
+        <v>344</v>
+      </c>
+      <c r="J8" t="s">
         <v>361</v>
-      </c>
-      <c r="G8" t="s">
-        <v>343</v>
-      </c>
-      <c r="H8" t="s">
-        <v>344</v>
-      </c>
-      <c r="I8" t="s">
-        <v>345</v>
-      </c>
-      <c r="J8" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s">
         <v>16</v>
       </c>
       <c r="D9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E9" t="s">
         <v>363</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>364</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
+        <v>342</v>
+      </c>
+      <c r="H9" t="s">
+        <v>343</v>
+      </c>
+      <c r="I9" t="s">
+        <v>344</v>
+      </c>
+      <c r="J9" t="s">
         <v>365</v>
-      </c>
-      <c r="G9" t="s">
-        <v>343</v>
-      </c>
-      <c r="H9" t="s">
-        <v>344</v>
-      </c>
-      <c r="I9" t="s">
-        <v>345</v>
-      </c>
-      <c r="J9" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="G10" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="H10" s="11" t="s">
+      <c r="I10" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="J10" s="11" t="s">
         <v>369</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="G11" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="J11" s="11" t="s">
         <v>372</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="G12" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="J12" s="11" t="s">
         <v>376</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="F13" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="G13" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="J13" s="11" t="s">
         <v>380</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4191,50 +4188,50 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="29" t="s">
         <v>384</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>385</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
@@ -4247,25 +4244,25 @@
         <v>28</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -4279,22 +4276,22 @@
         <v>28</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>387</v>
-      </c>
       <c r="F4" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>394</v>
-      </c>
       <c r="H4" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>391</v>
       </c>
       <c r="J4" s="4"/>
     </row>
@@ -4309,25 +4306,25 @@
         <v>28</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -4341,23 +4338,23 @@
         <v>28</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>387</v>
-      </c>
       <c r="F6" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -4371,25 +4368,25 @@
         <v>34</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="H7" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>405</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -4403,22 +4400,22 @@
         <v>34</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>403</v>
-      </c>
       <c r="F8" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H8" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="I8" s="9" t="s">
         <v>390</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>391</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -4433,22 +4430,22 @@
         <v>34</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>403</v>
-      </c>
       <c r="F9" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H9" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="I9" s="9" t="s">
         <v>390</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>391</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -4463,25 +4460,25 @@
         <v>34</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>403</v>
-      </c>
       <c r="F10" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>410</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -4495,28 +4492,28 @@
         <v>34</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>403</v>
-      </c>
       <c r="F11" s="9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>40</v>
@@ -4525,30 +4522,30 @@
         <v>45</v>
       </c>
       <c r="D12" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>415</v>
-      </c>
       <c r="G12" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H12" s="10" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>40</v>
@@ -4557,30 +4554,30 @@
         <v>45</v>
       </c>
       <c r="D13" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>414</v>
-      </c>
       <c r="F13" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>417</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>418</v>
       </c>
       <c r="H13" s="10" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>40</v>
@@ -4589,30 +4586,30 @@
         <v>45</v>
       </c>
       <c r="D14" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>414</v>
-      </c>
       <c r="F14" s="11" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H14" s="10" t="b">
         <v>0</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -4621,30 +4618,30 @@
         <v>45</v>
       </c>
       <c r="D15" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>414</v>
-      </c>
       <c r="F15" s="11" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H15" s="10" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>40</v>
@@ -4653,30 +4650,30 @@
         <v>45</v>
       </c>
       <c r="D16" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>414</v>
-      </c>
       <c r="F16" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>424</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>425</v>
       </c>
       <c r="H16" s="10" t="b">
         <v>0</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>40</v>
@@ -4685,28 +4682,28 @@
         <v>45</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>414</v>
-      </c>
       <c r="F17" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="10" t="b">
         <v>1</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>40</v>
@@ -4715,30 +4712,30 @@
         <v>45</v>
       </c>
       <c r="D18" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="F18" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="G18" s="12" t="s">
         <v>430</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>431</v>
       </c>
       <c r="H18" s="12" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>40</v>
@@ -4747,30 +4744,30 @@
         <v>45</v>
       </c>
       <c r="D19" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>429</v>
-      </c>
       <c r="F19" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="G19" s="12" t="s">
         <v>433</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>434</v>
       </c>
       <c r="H19" s="12" t="b">
         <v>0</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>40</v>
@@ -4779,30 +4776,30 @@
         <v>45</v>
       </c>
       <c r="D20" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>429</v>
-      </c>
       <c r="F20" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H20" s="12" t="b">
         <v>0</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>40</v>
@@ -4811,30 +4808,30 @@
         <v>45</v>
       </c>
       <c r="D21" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="E21" s="13" t="s">
-        <v>429</v>
-      </c>
       <c r="F21" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="G21" s="12" t="s">
         <v>438</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>439</v>
       </c>
       <c r="H21" s="12" t="b">
         <v>0</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>40</v>
@@ -4843,25 +4840,23 @@
         <v>45</v>
       </c>
       <c r="D22" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>429</v>
-      </c>
       <c r="F22" s="13" t="s">
-        <v>399</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>425</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="G22" s="12"/>
       <c r="H22" s="12" t="b">
         <v>1</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -4898,54 +4893,54 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="29" t="s">
         <v>444</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>445</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
     </row>
     <row r="3" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
@@ -4958,26 +4953,26 @@
         <v>50</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>446</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>447</v>
       </c>
       <c r="F3" s="4">
         <v>0</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J3" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -4991,28 +4986,28 @@
         <v>50</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>446</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>447</v>
       </c>
       <c r="F4" s="5">
         <v>1</v>
       </c>
       <c r="G4" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>452</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -5026,28 +5021,28 @@
         <v>50</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>446</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>447</v>
       </c>
       <c r="F5" s="4">
         <v>2</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>454</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -5061,28 +5056,28 @@
         <v>50</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>446</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>447</v>
       </c>
       <c r="F6" s="5">
         <v>3</v>
       </c>
       <c r="G6" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>457</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5096,25 +5091,25 @@
         <v>57</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>459</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>460</v>
       </c>
       <c r="F7" s="6">
         <v>0</v>
       </c>
       <c r="G7" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="K7" s="6" t="s">
         <v>461</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5128,28 +5123,28 @@
         <v>57</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>459</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>460</v>
       </c>
       <c r="F8" s="6">
         <v>1</v>
       </c>
       <c r="G8" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="I8" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="K8" s="6" t="s">
         <v>464</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5163,28 +5158,28 @@
         <v>57</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>459</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>460</v>
       </c>
       <c r="F9" s="6">
         <v>2</v>
       </c>
       <c r="G9" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>466</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5198,28 +5193,28 @@
         <v>57</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>459</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>460</v>
       </c>
       <c r="F10" s="6">
         <v>3</v>
       </c>
       <c r="G10" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="I10" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="K10" s="6" t="s">
         <v>469</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5233,25 +5228,25 @@
         <v>62</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>471</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>472</v>
       </c>
       <c r="F11" s="6">
         <v>0</v>
       </c>
       <c r="G11" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="K11" s="6" t="s">
         <v>473</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5265,28 +5260,28 @@
         <v>62</v>
       </c>
       <c r="D12" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>471</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>472</v>
       </c>
       <c r="F12" s="6">
         <v>1</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="I12" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="K12" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5300,28 +5295,28 @@
         <v>62</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>471</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>472</v>
       </c>
       <c r="F13" s="6">
         <v>2</v>
       </c>
       <c r="G13" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="K13" s="6" t="s">
         <v>478</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5335,28 +5330,28 @@
         <v>62</v>
       </c>
       <c r="D14" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>471</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>472</v>
       </c>
       <c r="F14" s="6">
         <v>3</v>
       </c>
       <c r="G14" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="I14" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="K14" s="6" t="s">
         <v>481</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -5389,350 +5384,350 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>126</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>263</v>
-      </c>
       <c r="F1" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>534</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="29" t="s">
         <v>484</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="I1" s="22" t="s">
-        <v>535</v>
-      </c>
-      <c r="J1" s="22" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>485</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
     </row>
     <row r="3" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>489</v>
       </c>
       <c r="F3" s="7">
         <v>2</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>491</v>
-      </c>
       <c r="I3" s="21" t="s">
+        <v>536</v>
+      </c>
+      <c r="J3" s="21" t="s">
         <v>537</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="21" t="s">
+        <v>538</v>
+      </c>
+      <c r="J4" s="21" t="s">
         <v>539</v>
-      </c>
-      <c r="J4" s="21" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F5" s="7">
         <v>0</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>496</v>
-      </c>
       <c r="I5" s="21" t="s">
+        <v>540</v>
+      </c>
+      <c r="J5" s="21" t="s">
         <v>541</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>498</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>499</v>
       </c>
       <c r="F6" s="8">
         <v>2</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>501</v>
-      </c>
       <c r="I6" s="21" t="s">
+        <v>542</v>
+      </c>
+      <c r="J6" s="21" t="s">
         <v>543</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F7" s="8">
         <v>1</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I7" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="J7" s="21" t="s">
         <v>545</v>
-      </c>
-      <c r="J7" s="21" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F8" s="8">
         <v>0</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I8" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="J8" s="21" t="s">
         <v>547</v>
-      </c>
-      <c r="J8" s="21" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>507</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>508</v>
       </c>
       <c r="F9" s="8">
         <v>2</v>
       </c>
       <c r="G9" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="H9" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>510</v>
-      </c>
       <c r="I9" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="J9" s="21" t="s">
         <v>549</v>
-      </c>
-      <c r="J9" s="21" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F10" s="8">
         <v>1</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I10" s="21" t="s">
+        <v>550</v>
+      </c>
+      <c r="J10" s="21" t="s">
         <v>551</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
       </c>
       <c r="G11" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>515</v>
-      </c>
       <c r="I11" s="21" t="s">
+        <v>552</v>
+      </c>
+      <c r="J11" s="21" t="s">
         <v>553</v>
-      </c>
-      <c r="J11" s="21" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>517</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>518</v>
       </c>
       <c r="F12" s="8">
         <v>2</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="I12" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="J12" s="21" t="s">
         <v>555</v>
-      </c>
-      <c r="J12" s="21" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F13" s="8">
         <v>1</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="I13" s="21" t="s">
+        <v>556</v>
+      </c>
+      <c r="J13" s="21" t="s">
         <v>557</v>
-      </c>
-      <c r="J13" s="21" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F14" s="8">
         <v>0</v>
       </c>
       <c r="G14" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>524</v>
-      </c>
       <c r="I14" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="J14" s="21" t="s">
         <v>559</v>
-      </c>
-      <c r="J14" s="21" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -5763,18 +5758,18 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
@@ -6193,18 +6188,18 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
@@ -6222,7 +6217,7 @@
       <c r="E20" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F20" s="30" t="s">
+      <c r="F20" s="24" t="s">
         <v>12</v>
       </c>
     </row>
@@ -6240,7 +6235,7 @@
         <v>91</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="210" x14ac:dyDescent="0.2">
@@ -6257,9 +6252,9 @@
         <v>95</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="F22" s="29" t="s">
+        <v>563</v>
+      </c>
+      <c r="F22" s="23" t="s">
         <v>564</v>
       </c>
     </row>
@@ -6277,10 +6272,10 @@
         <v>95</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>563</v>
-      </c>
-      <c r="F23" s="29" t="s">
-        <v>565</v>
+        <v>561</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.2">
@@ -6301,18 +6296,18 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="23" t="s">
-        <v>533</v>
-      </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
+      <c r="A26" s="25" t="s">
+        <v>532</v>
+      </c>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
@@ -6370,13 +6365,13 @@
         <v>119</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C30" s="11" t="s">
+        <v>528</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>529</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>530</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>120</v>
@@ -6390,7 +6385,7 @@
         <v>122</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>123</v>
@@ -6400,18 +6395,18 @@
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
@@ -6506,30 +6501,28 @@
         <v>151</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>534</v>
-      </c>
-      <c r="D39" s="11" t="s">
+        <v>533</v>
+      </c>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11" t="s">
         <v>152</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.2">
       <c r="A40" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="B40" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="C40" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="D40" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="E40" s="11" t="s">
         <v>157</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/Logic/Question_Binder_Sep30.xlsx
+++ b/Logic/Question_Binder_Sep30.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gosciminski/Documents/GitHub/M-GRAT/Logic/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3720676F-6F82-B94B-A282-53CB36FF9783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6000335A-8622-B244-8777-0A0FB0A5689D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21740" yWindow="-20160" windowWidth="33720" windowHeight="19380" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21820" yWindow="-20440" windowWidth="30800" windowHeight="18400" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>

--- a/Logic/Question_Binder_Sep30.xlsx
+++ b/Logic/Question_Binder_Sep30.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gosciminski/Documents/GitHub/M-GRAT/Logic/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6000335A-8622-B244-8777-0A0FB0A5689D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FBCB42-3CA9-484F-BB39-98CE02A952F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21820" yWindow="-20440" windowWidth="30800" windowHeight="18400" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16420" yWindow="-20120" windowWidth="30800" windowHeight="18400" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -1762,12 +1762,12 @@
 • APM Stage 1 (Digital Maintenance Foundation): Requires AD-1-REG, AD-1-CRIT, CM-1-LF, RP-1-FC = MET
 • APM Stage 2 (APM Foundation): Requires Stage 1 Met + AD-2-CLAS, CM-2-HLTH, RP-2-RS, RP-3-FMEA = MET
 • APM Stage 3 (Maintenance Optimisation (CBM+)): Requires Stage 2 Met + AD-2-HIER, IC-3-METB, CM-2-TRIG, CM-3-IOT, CM-3-MVAR, SC-4-OPT = MET
-• APM Stage 4 (Prescriptive Reliability): Requires Stage 3 Met + CM-4-PRED, CM-6-LCFDBK, RP-4-RCBF = MET
+• APM Stage 4 (Prescriptive Reliability): Requires Stage 3 Met + CM-4-PRED, CM-6-LCFDBK, CM-5-RCBF = MET
 • APM Stage 5 (Reliability Enterprise): Requires Stage 4 Met + RP-5-FGOV = MET
 * If Stage 1 gating milestones are not all Met, Current Stage = APM 1 (In Progress).</t>
   </si>
   <si>
-    <t>Notes: KG - I removed the CM-2-MON milestone because 1) Monitor isn't required for APM at all and 2) that milestone has no question associated with it in the binder so it was breaking this stage calculation.  I think we could remove more.  Removed CM-5-RCBFbc it's not covered in questions.
+    <t>Notes: KG - I removed the CM-2-MON milestone because 1) Monitor isn't required for APM at all and 2) that milestone has no question associated with it in the binder so it was breaking this stage calculation.  I think we could remove more.  Removed RP-4-RCBF (stage 4) bc it's not covered in questions.
 Open issue: We should  consider a different way of detecting current stage for APM since there are so many different ways to do things.  Or possibly we need to genericize the milestones so they say things like "a mechanism triggers work based on condition signals" and then we explain the multiple ways to do that.</t>
   </si>
 </sst>
